--- a/WebApi/excel_emg_tradding.xlsx
+++ b/WebApi/excel_emg_tradding.xlsx
@@ -48,9 +48,6 @@
     <t>TAB</t>
   </si>
   <si>
-    <t>總消耗量</t>
-  </si>
-  <si>
     <t>病人姓名</t>
   </si>
   <si>
@@ -128,6 +125,10 @@
   </si>
   <si>
     <t>領藥號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上期結存</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -438,13 +439,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -469,6 +467,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -517,20 +530,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -838,7 +842,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -850,164 +854,166 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.625" customWidth="1"/>
-    <col min="7" max="9" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="9.625" customWidth="1"/>
-    <col min="11" max="11" width="26.25" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="31" customWidth="1"/>
+    <col min="11" max="11" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
         <v>728</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>22</v>
+      <c r="H2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2">
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1">
         <v>123</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>22</v>
+      <c r="J3" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="22">
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="26">
         <v>123</v>
       </c>
-      <c r="J4" s="23"/>
-      <c r="K4" s="24"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="I5" s="16">
         <v>123</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="25"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="29"/>
     </row>
-    <row r="6" spans="1:11" s="30" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+    <row r="6" spans="1:11" s="13" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1028,7 @@
     <mergeCell ref="I5:K5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>